--- a/inputs/A1_Outputs/A1_Outputs_VGB/A-O_Demand.xlsx
+++ b/inputs/A1_Outputs/A1_Outputs_VGB/A-O_Demand.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand_Projection" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profiles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Demand_Projection" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Profiles" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -750,88 +750,88 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>558.829268292683</v>
+        <v>564.3</v>
       </c>
       <c r="J2" t="n">
-        <v>572.8</v>
+        <v>544.72</v>
       </c>
       <c r="K2" t="n">
-        <v>595.66</v>
+        <v>552.89</v>
       </c>
       <c r="L2" t="n">
-        <v>619.25</v>
+        <v>561.1799999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>643.61</v>
+        <v>569.6</v>
       </c>
       <c r="N2" t="n">
-        <v>668.75</v>
+        <v>578.15</v>
       </c>
       <c r="O2" t="n">
-        <v>694.6900000000001</v>
+        <v>586.8200000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>721.46</v>
+        <v>594.6799999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>749.09</v>
+        <v>637.38</v>
       </c>
       <c r="R2" t="n">
-        <v>777.59</v>
+        <v>683.14</v>
       </c>
       <c r="S2" t="n">
-        <v>806.99</v>
+        <v>732.1900000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>837.33</v>
+        <v>784.76</v>
       </c>
       <c r="U2" t="n">
-        <v>868.62</v>
+        <v>841.11</v>
       </c>
       <c r="V2" t="n">
-        <v>907.0599999999999</v>
+        <v>901.5</v>
       </c>
       <c r="W2" t="n">
-        <v>946.55</v>
+        <v>966.23</v>
       </c>
       <c r="X2" t="n">
-        <v>987.13</v>
+        <v>1035.61</v>
       </c>
       <c r="Y2" t="n">
-        <v>1028.81</v>
+        <v>1109.96</v>
       </c>
       <c r="Z2" t="n">
-        <v>1071.62</v>
+        <v>1189.66</v>
       </c>
       <c r="AA2" t="n">
-        <v>1115.59</v>
+        <v>1228.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1160.75</v>
+        <v>1268</v>
       </c>
       <c r="AC2" t="n">
-        <v>1207.12</v>
+        <v>1309.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>1254.73</v>
+        <v>1351.49</v>
       </c>
       <c r="AE2" t="n">
-        <v>1303.61</v>
+        <v>1395.28</v>
       </c>
       <c r="AF2" t="n">
-        <v>1353.79</v>
+        <v>1440.49</v>
       </c>
       <c r="AG2" t="n">
-        <v>1405.3</v>
+        <v>1487.16</v>
       </c>
       <c r="AH2" t="n">
-        <v>1458.17</v>
+        <v>1535.34</v>
       </c>
       <c r="AI2" t="n">
-        <v>1512.43</v>
+        <v>1585.09</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1568.11</v>
+        <v>1636.45</v>
       </c>
     </row>
     <row r="3">
@@ -874,88 +874,88 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>41.39512195121952</v>
+        <v>42.81</v>
       </c>
       <c r="J3" t="n">
-        <v>42.43</v>
+        <v>44.02</v>
       </c>
       <c r="K3" t="n">
-        <v>44.71</v>
+        <v>45.54</v>
       </c>
       <c r="L3" t="n">
-        <v>47.09</v>
+        <v>47.12</v>
       </c>
       <c r="M3" t="n">
-        <v>49.59</v>
+        <v>48.75</v>
       </c>
       <c r="N3" t="n">
-        <v>52.21</v>
+        <v>54.55</v>
       </c>
       <c r="O3" t="n">
-        <v>54.95</v>
+        <v>56.11</v>
       </c>
       <c r="P3" t="n">
-        <v>57.82</v>
+        <v>59.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>60.82</v>
+        <v>64.63</v>
       </c>
       <c r="R3" t="n">
-        <v>63.97</v>
+        <v>67.48</v>
       </c>
       <c r="S3" t="n">
-        <v>67.27</v>
+        <v>70.38</v>
       </c>
       <c r="T3" t="n">
-        <v>70.72</v>
+        <v>73.3</v>
       </c>
       <c r="U3" t="n">
-        <v>74.33</v>
+        <v>75.14</v>
       </c>
       <c r="V3" t="n">
-        <v>78.44</v>
+        <v>77.02</v>
       </c>
       <c r="W3" t="n">
-        <v>82.73</v>
+        <v>78.95</v>
       </c>
       <c r="X3" t="n">
-        <v>87.19</v>
+        <v>80.91</v>
       </c>
       <c r="Y3" t="n">
-        <v>91.84</v>
+        <v>82.94</v>
       </c>
       <c r="Z3" t="n">
-        <v>96.67</v>
+        <v>85</v>
       </c>
       <c r="AA3" t="n">
-        <v>101.71</v>
+        <v>87.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>106.95</v>
+        <v>89.31</v>
       </c>
       <c r="AC3" t="n">
-        <v>112.4</v>
+        <v>91.53</v>
       </c>
       <c r="AD3" t="n">
-        <v>118.08</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="AE3" t="n">
-        <v>123.98</v>
+        <v>96.16</v>
       </c>
       <c r="AF3" t="n">
-        <v>130.12</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>136.5</v>
+        <v>101.02</v>
       </c>
       <c r="AH3" t="n">
-        <v>143.14</v>
+        <v>103.55</v>
       </c>
       <c r="AI3" t="n">
-        <v>150.05</v>
+        <v>106.14</v>
       </c>
       <c r="AJ3" t="n">
-        <v>157.22</v>
+        <v>108.78</v>
       </c>
     </row>
     <row r="4">
@@ -998,88 +998,88 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2237.268292682927</v>
+        <v>2599.63</v>
       </c>
       <c r="J4" t="n">
-        <v>2293.2</v>
+        <v>2737.32</v>
       </c>
       <c r="K4" t="n">
-        <v>2374.59</v>
+        <v>2846.81</v>
       </c>
       <c r="L4" t="n">
-        <v>2458.36</v>
+        <v>2960.69</v>
       </c>
       <c r="M4" t="n">
-        <v>2544.56</v>
+        <v>3079.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2633.26</v>
+        <v>3202.28</v>
       </c>
       <c r="O4" t="n">
-        <v>2724.53</v>
+        <v>3330.37</v>
       </c>
       <c r="P4" t="n">
-        <v>2818.44</v>
+        <v>3463.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>2915.05</v>
+        <v>3602.13</v>
       </c>
       <c r="R4" t="n">
-        <v>3014.44</v>
+        <v>3746.21</v>
       </c>
       <c r="S4" t="n">
-        <v>3116.67</v>
+        <v>3896.06</v>
       </c>
       <c r="T4" t="n">
-        <v>3221.84</v>
+        <v>4052.68</v>
       </c>
       <c r="U4" t="n">
-        <v>3330</v>
+        <v>4168.59</v>
       </c>
       <c r="V4" t="n">
-        <v>3458.25</v>
+        <v>4287.81</v>
       </c>
       <c r="W4" t="n">
-        <v>3589.65</v>
+        <v>4410.01</v>
       </c>
       <c r="X4" t="n">
-        <v>3724.26</v>
+        <v>4536.14</v>
       </c>
       <c r="Y4" t="n">
-        <v>3862.15</v>
+        <v>4665.87</v>
       </c>
       <c r="Z4" t="n">
-        <v>4003.39</v>
+        <v>4799.32</v>
       </c>
       <c r="AA4" t="n">
-        <v>4148.04</v>
+        <v>4936.58</v>
       </c>
       <c r="AB4" t="n">
-        <v>4296.19</v>
+        <v>5077.76</v>
       </c>
       <c r="AC4" t="n">
-        <v>4447.89</v>
+        <v>5222.99</v>
       </c>
       <c r="AD4" t="n">
-        <v>4603.23</v>
+        <v>5372.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>4762.29</v>
+        <v>5526.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>4925.13</v>
+        <v>5684.06</v>
       </c>
       <c r="AG4" t="n">
-        <v>5091.84</v>
+        <v>5846.62</v>
       </c>
       <c r="AH4" t="n">
-        <v>5262.5</v>
+        <v>6013.84</v>
       </c>
       <c r="AI4" t="n">
-        <v>5437.2</v>
+        <v>6185.83</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5616</v>
+        <v>6362.75</v>
       </c>
     </row>
     <row r="5">
@@ -1122,88 +1122,88 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>4.13658536585366</v>
+        <v>3.87</v>
       </c>
       <c r="J5" t="n">
-        <v>4.24</v>
+        <v>4.13</v>
       </c>
       <c r="K5" t="n">
-        <v>4.37</v>
+        <v>4.49</v>
       </c>
       <c r="L5" t="n">
-        <v>4.49</v>
+        <v>4.89</v>
       </c>
       <c r="M5" t="n">
-        <v>4.62</v>
+        <v>5.31</v>
       </c>
       <c r="N5" t="n">
-        <v>4.75</v>
+        <v>5.78</v>
       </c>
       <c r="O5" t="n">
-        <v>4.89</v>
+        <v>6.29</v>
       </c>
       <c r="P5" t="n">
-        <v>5.02</v>
+        <v>6.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.16</v>
+        <v>6.88</v>
       </c>
       <c r="R5" t="n">
-        <v>5.3</v>
+        <v>6.93</v>
       </c>
       <c r="S5" t="n">
-        <v>5.45</v>
+        <v>6.96</v>
       </c>
       <c r="T5" t="n">
-        <v>5.59</v>
+        <v>7.01</v>
       </c>
       <c r="U5" t="n">
-        <v>5.74</v>
+        <v>7.05</v>
       </c>
       <c r="V5" t="n">
-        <v>5.94</v>
+        <v>7.1</v>
       </c>
       <c r="W5" t="n">
-        <v>6.14</v>
+        <v>7.15</v>
       </c>
       <c r="X5" t="n">
-        <v>6.34</v>
+        <v>7.19</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.54</v>
+        <v>7.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.74</v>
+        <v>7.27</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.95</v>
+        <v>7.32</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.16</v>
+        <v>7.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.38</v>
+        <v>7.41</v>
       </c>
       <c r="AD5" t="n">
-        <v>7.59</v>
+        <v>7.45</v>
       </c>
       <c r="AE5" t="n">
-        <v>7.81</v>
+        <v>7.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.029999999999999</v>
+        <v>7.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>8.25</v>
+        <v>7.6</v>
       </c>
       <c r="AH5" t="n">
-        <v>8.48</v>
+        <v>7.65</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.710000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8.94</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="6">
@@ -1246,88 +1246,88 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>339.4341463414635</v>
+        <v>301.16</v>
       </c>
       <c r="J6" t="n">
-        <v>347.92</v>
+        <v>323.5</v>
       </c>
       <c r="K6" t="n">
-        <v>359.86</v>
+        <v>334.18</v>
       </c>
       <c r="L6" t="n">
-        <v>372.1</v>
+        <v>344.84</v>
       </c>
       <c r="M6" t="n">
-        <v>384.66</v>
+        <v>355.49</v>
       </c>
       <c r="N6" t="n">
-        <v>397.53</v>
+        <v>366.16</v>
       </c>
       <c r="O6" t="n">
-        <v>410.73</v>
+        <v>376.81</v>
       </c>
       <c r="P6" t="n">
-        <v>424.27</v>
+        <v>391.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>438.14</v>
+        <v>431.49</v>
       </c>
       <c r="R6" t="n">
-        <v>452.37</v>
+        <v>476.15</v>
       </c>
       <c r="S6" t="n">
-        <v>466.95</v>
+        <v>525.4299999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>481.9</v>
+        <v>579.8099999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>497.22</v>
+        <v>639.8200000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>516.3099999999999</v>
+        <v>667.2</v>
       </c>
       <c r="W6" t="n">
-        <v>535.77</v>
+        <v>695.76</v>
       </c>
       <c r="X6" t="n">
-        <v>555.6</v>
+        <v>725.54</v>
       </c>
       <c r="Y6" t="n">
-        <v>575.8200000000001</v>
+        <v>756.59</v>
       </c>
       <c r="Z6" t="n">
-        <v>596.42</v>
+        <v>788.97</v>
       </c>
       <c r="AA6" t="n">
-        <v>617.41</v>
+        <v>829.21</v>
       </c>
       <c r="AB6" t="n">
-        <v>638.8</v>
+        <v>871.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>660.6</v>
+        <v>915.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>682.8</v>
+        <v>962.66</v>
       </c>
       <c r="AE6" t="n">
-        <v>705.4299999999999</v>
+        <v>1011.76</v>
       </c>
       <c r="AF6" t="n">
-        <v>728.48</v>
+        <v>1063.36</v>
       </c>
       <c r="AG6" t="n">
-        <v>751.95</v>
+        <v>1117.59</v>
       </c>
       <c r="AH6" t="n">
-        <v>775.87</v>
+        <v>1174.58</v>
       </c>
       <c r="AI6" t="n">
-        <v>800.23</v>
+        <v>1234.49</v>
       </c>
       <c r="AJ6" t="n">
-        <v>825.04</v>
+        <v>1297.45</v>
       </c>
     </row>
     <row r="7">
@@ -1370,88 +1370,88 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>310.4585365853659</v>
+        <v>285.84</v>
       </c>
       <c r="J7" t="n">
-        <v>318.22</v>
+        <v>293.91</v>
       </c>
       <c r="K7" t="n">
-        <v>334.51</v>
+        <v>315.87</v>
       </c>
       <c r="L7" t="n">
-        <v>351.54</v>
+        <v>334.12</v>
       </c>
       <c r="M7" t="n">
-        <v>369.33</v>
+        <v>347.35</v>
       </c>
       <c r="N7" t="n">
-        <v>387.92</v>
+        <v>358.02</v>
       </c>
       <c r="O7" t="n">
-        <v>407.35</v>
+        <v>371.44</v>
       </c>
       <c r="P7" t="n">
-        <v>427.64</v>
+        <v>381.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>448.83</v>
+        <v>394.06</v>
       </c>
       <c r="R7" t="n">
-        <v>470.97</v>
+        <v>405.1</v>
       </c>
       <c r="S7" t="n">
-        <v>494.08</v>
+        <v>418.46</v>
       </c>
       <c r="T7" t="n">
-        <v>518.22</v>
+        <v>432.32</v>
       </c>
       <c r="U7" t="n">
-        <v>543.42</v>
+        <v>446.67</v>
       </c>
       <c r="V7" t="n">
-        <v>572.33</v>
+        <v>459.98</v>
       </c>
       <c r="W7" t="n">
-        <v>602.36</v>
+        <v>477.37</v>
       </c>
       <c r="X7" t="n">
-        <v>633.55</v>
+        <v>493.17</v>
       </c>
       <c r="Y7" t="n">
-        <v>665.95</v>
+        <v>504.56</v>
       </c>
       <c r="Z7" t="n">
-        <v>699.6</v>
+        <v>516.21</v>
       </c>
       <c r="AA7" t="n">
-        <v>734.53</v>
+        <v>528.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>770.8</v>
+        <v>540.34</v>
       </c>
       <c r="AC7" t="n">
-        <v>808.45</v>
+        <v>552.87</v>
       </c>
       <c r="AD7" t="n">
-        <v>847.53</v>
+        <v>565.65</v>
       </c>
       <c r="AE7" t="n">
-        <v>888.08</v>
+        <v>578.77</v>
       </c>
       <c r="AF7" t="n">
-        <v>930.15</v>
+        <v>592.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>973.8</v>
+        <v>605.8200000000001</v>
       </c>
       <c r="AH7" t="n">
-        <v>1019.08</v>
+        <v>619.8099999999999</v>
       </c>
       <c r="AI7" t="n">
-        <v>1066.04</v>
+        <v>634.13</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1114.75</v>
+        <v>648.78</v>
       </c>
     </row>
     <row r="8">
@@ -1494,88 +1494,88 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>49.67804878048781</v>
+        <v>44.28</v>
       </c>
       <c r="J8" t="n">
-        <v>50.92</v>
+        <v>46.05</v>
       </c>
       <c r="K8" t="n">
-        <v>53.26</v>
+        <v>47.63</v>
       </c>
       <c r="L8" t="n">
-        <v>55.69</v>
+        <v>49.09</v>
       </c>
       <c r="M8" t="n">
-        <v>58.22</v>
+        <v>50.23</v>
       </c>
       <c r="N8" t="n">
-        <v>60.85</v>
+        <v>51.95</v>
       </c>
       <c r="O8" t="n">
-        <v>63.58</v>
+        <v>53.66</v>
       </c>
       <c r="P8" t="n">
-        <v>66.42</v>
+        <v>55.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>69.37</v>
+        <v>57.01</v>
       </c>
       <c r="R8" t="n">
-        <v>72.43000000000001</v>
+        <v>58.62</v>
       </c>
       <c r="S8" t="n">
-        <v>75.61</v>
+        <v>60.19</v>
       </c>
       <c r="T8" t="n">
-        <v>78.91</v>
+        <v>61.7</v>
       </c>
       <c r="U8" t="n">
-        <v>82.34</v>
+        <v>63.1</v>
       </c>
       <c r="V8" t="n">
-        <v>86.34999999999999</v>
+        <v>64.44</v>
       </c>
       <c r="W8" t="n">
-        <v>90.48999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>94.77</v>
+        <v>66.78</v>
       </c>
       <c r="Y8" t="n">
-        <v>99.19</v>
+        <v>67.84</v>
       </c>
       <c r="Z8" t="n">
-        <v>103.75</v>
+        <v>68.81</v>
       </c>
       <c r="AA8" t="n">
-        <v>108.47</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>113.33</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>118.36</v>
+        <v>71.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>123.55</v>
+        <v>72.83</v>
       </c>
       <c r="AE8" t="n">
-        <v>128.91</v>
+        <v>73.86</v>
       </c>
       <c r="AF8" t="n">
-        <v>134.43</v>
+        <v>74.92</v>
       </c>
       <c r="AG8" t="n">
-        <v>140.14</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="AH8" t="n">
-        <v>146.02</v>
+        <v>77.08</v>
       </c>
       <c r="AI8" t="n">
-        <v>152.1</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="AJ8" t="n">
-        <v>158.37</v>
+        <v>79.29000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1618,88 +1618,88 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>82.79024390243903</v>
+        <v>86.09</v>
       </c>
       <c r="J9" t="n">
-        <v>84.86</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>89.93000000000001</v>
+        <v>96.06</v>
       </c>
       <c r="L9" t="n">
-        <v>95.27</v>
+        <v>100.93</v>
       </c>
       <c r="M9" t="n">
-        <v>100.91</v>
+        <v>106.02</v>
       </c>
       <c r="N9" t="n">
-        <v>106.85</v>
+        <v>111.39</v>
       </c>
       <c r="O9" t="n">
-        <v>113.11</v>
+        <v>117.02</v>
       </c>
       <c r="P9" t="n">
-        <v>119.71</v>
+        <v>122.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>126.67</v>
+        <v>129.19</v>
       </c>
       <c r="R9" t="n">
-        <v>133.99</v>
+        <v>135.75</v>
       </c>
       <c r="S9" t="n">
-        <v>141.71</v>
+        <v>142.65</v>
       </c>
       <c r="T9" t="n">
-        <v>149.84</v>
+        <v>149.88</v>
       </c>
       <c r="U9" t="n">
-        <v>158.41</v>
+        <v>157.5</v>
       </c>
       <c r="V9" t="n">
-        <v>167.78</v>
+        <v>165.5</v>
       </c>
       <c r="W9" t="n">
-        <v>177.58</v>
+        <v>173.91</v>
       </c>
       <c r="X9" t="n">
-        <v>187.83</v>
+        <v>182.74</v>
       </c>
       <c r="Y9" t="n">
-        <v>198.55</v>
+        <v>192.02</v>
       </c>
       <c r="Z9" t="n">
-        <v>209.76</v>
+        <v>201.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>221.48</v>
+        <v>212.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>233.73</v>
+        <v>222.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>246.54</v>
+        <v>234.09</v>
       </c>
       <c r="AD9" t="n">
-        <v>259.91</v>
+        <v>245.99</v>
       </c>
       <c r="AE9" t="n">
-        <v>273.89</v>
+        <v>258.46</v>
       </c>
       <c r="AF9" t="n">
-        <v>288.49</v>
+        <v>271.59</v>
       </c>
       <c r="AG9" t="n">
-        <v>303.73</v>
+        <v>285.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>319.65</v>
+        <v>299.85</v>
       </c>
       <c r="AI9" t="n">
-        <v>336.28</v>
+        <v>315.06</v>
       </c>
       <c r="AJ9" t="n">
-        <v>353.63</v>
+        <v>331.06</v>
       </c>
     </row>
     <row r="10">
@@ -1742,88 +1742,88 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>115.9024390243902</v>
+        <v>129.57</v>
       </c>
       <c r="J10" t="n">
-        <v>118.8</v>
+        <v>128.37</v>
       </c>
       <c r="K10" t="n">
-        <v>123.85</v>
+        <v>141.99</v>
       </c>
       <c r="L10" t="n">
-        <v>129.07</v>
+        <v>153.25</v>
       </c>
       <c r="M10" t="n">
-        <v>134.47</v>
+        <v>161.68</v>
       </c>
       <c r="N10" t="n">
-        <v>140.06</v>
+        <v>168.44</v>
       </c>
       <c r="O10" t="n">
-        <v>145.85</v>
+        <v>175.6</v>
       </c>
       <c r="P10" t="n">
-        <v>151.84</v>
+        <v>183.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>158.04</v>
+        <v>192.77</v>
       </c>
       <c r="R10" t="n">
-        <v>164.46</v>
+        <v>201.77</v>
       </c>
       <c r="S10" t="n">
-        <v>171.1</v>
+        <v>211.19</v>
       </c>
       <c r="T10" t="n">
-        <v>177.96</v>
+        <v>221.05</v>
       </c>
       <c r="U10" t="n">
-        <v>185.06</v>
+        <v>231.38</v>
       </c>
       <c r="V10" t="n">
-        <v>193.44</v>
+        <v>242.18</v>
       </c>
       <c r="W10" t="n">
-        <v>202.06</v>
+        <v>253.49</v>
       </c>
       <c r="X10" t="n">
-        <v>210.93</v>
+        <v>265.33</v>
       </c>
       <c r="Y10" t="n">
-        <v>220.06</v>
+        <v>277.72</v>
       </c>
       <c r="Z10" t="n">
-        <v>229.44</v>
+        <v>290.69</v>
       </c>
       <c r="AA10" t="n">
-        <v>239.09</v>
+        <v>304.26</v>
       </c>
       <c r="AB10" t="n">
-        <v>249.01</v>
+        <v>318.47</v>
       </c>
       <c r="AC10" t="n">
-        <v>259.21</v>
+        <v>333.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>269.7</v>
+        <v>348.88</v>
       </c>
       <c r="AE10" t="n">
-        <v>280.48</v>
+        <v>365.17</v>
       </c>
       <c r="AF10" t="n">
-        <v>291.57</v>
+        <v>382.23</v>
       </c>
       <c r="AG10" t="n">
-        <v>302.96</v>
+        <v>400.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>314.66</v>
+        <v>418.76</v>
       </c>
       <c r="AI10" t="n">
-        <v>326.69</v>
+        <v>438.32</v>
       </c>
       <c r="AJ10" t="n">
-        <v>339.06</v>
+        <v>458.78</v>
       </c>
     </row>
     <row r="11">
@@ -1866,88 +1866,88 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>57.95121951219512</v>
+        <v>47.17</v>
       </c>
       <c r="J11" t="n">
-        <v>59.4</v>
+        <v>50.24</v>
       </c>
       <c r="K11" t="n">
-        <v>62.77</v>
+        <v>52.45</v>
       </c>
       <c r="L11" t="n">
-        <v>66.31</v>
+        <v>54.71</v>
       </c>
       <c r="M11" t="n">
-        <v>70.03</v>
+        <v>57.24</v>
       </c>
       <c r="N11" t="n">
-        <v>73.94</v>
+        <v>59.71</v>
       </c>
       <c r="O11" t="n">
-        <v>78.05</v>
+        <v>62.26</v>
       </c>
       <c r="P11" t="n">
-        <v>82.36</v>
+        <v>65.09</v>
       </c>
       <c r="Q11" t="n">
-        <v>86.89</v>
+        <v>68.11</v>
       </c>
       <c r="R11" t="n">
-        <v>91.66</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>96.66</v>
+        <v>74.2</v>
       </c>
       <c r="T11" t="n">
-        <v>101.91</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>107.42</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>113.34</v>
+        <v>84.44</v>
       </c>
       <c r="W11" t="n">
-        <v>119.49</v>
+        <v>88.19</v>
       </c>
       <c r="X11" t="n">
-        <v>125.9</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>132.57</v>
+        <v>96.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>139.51</v>
+        <v>100.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>146.74</v>
+        <v>105.18</v>
       </c>
       <c r="AB11" t="n">
-        <v>154.25</v>
+        <v>110</v>
       </c>
       <c r="AC11" t="n">
-        <v>162.07</v>
+        <v>115.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>170.2</v>
+        <v>120.24</v>
       </c>
       <c r="AE11" t="n">
-        <v>178.66</v>
+        <v>125.79</v>
       </c>
       <c r="AF11" t="n">
-        <v>187.45</v>
+        <v>131.61</v>
       </c>
       <c r="AG11" t="n">
-        <v>196.59</v>
+        <v>137.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>206.1</v>
+        <v>143.37</v>
       </c>
       <c r="AI11" t="n">
-        <v>215.97</v>
+        <v>149.72</v>
       </c>
       <c r="AJ11" t="n">
-        <v>226.23</v>
+        <v>156.43</v>
       </c>
     </row>
     <row r="12">
@@ -1990,88 +1990,88 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>37.25853658536585</v>
+        <v>43.15</v>
       </c>
       <c r="J12" t="n">
-        <v>38.19</v>
+        <v>46.21</v>
       </c>
       <c r="K12" t="n">
-        <v>40.2</v>
+        <v>49.99</v>
       </c>
       <c r="L12" t="n">
-        <v>42.3</v>
+        <v>51.81</v>
       </c>
       <c r="M12" t="n">
-        <v>44.5</v>
+        <v>53.5</v>
       </c>
       <c r="N12" t="n">
-        <v>46.8</v>
+        <v>55.47</v>
       </c>
       <c r="O12" t="n">
-        <v>49.21</v>
+        <v>57.48</v>
       </c>
       <c r="P12" t="n">
-        <v>51.73</v>
+        <v>59.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>54.37</v>
+        <v>61.25</v>
       </c>
       <c r="R12" t="n">
-        <v>57.13</v>
+        <v>63.39</v>
       </c>
       <c r="S12" t="n">
-        <v>60.02</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>63.03</v>
+        <v>67.42</v>
       </c>
       <c r="U12" t="n">
-        <v>66.19</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>69.68000000000001</v>
+        <v>73.22</v>
       </c>
       <c r="W12" t="n">
-        <v>73.31</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>77.08</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>80.98999999999999</v>
+        <v>79.94</v>
       </c>
       <c r="Z12" t="n">
-        <v>85.04000000000001</v>
+        <v>82.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>89.26000000000001</v>
+        <v>84.89</v>
       </c>
       <c r="AB12" t="n">
-        <v>93.63</v>
+        <v>87.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>98.16</v>
+        <v>90.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>102.87</v>
+        <v>92.89</v>
       </c>
       <c r="AE12" t="n">
-        <v>107.75</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="AF12" t="n">
-        <v>112.81</v>
+        <v>98.63</v>
       </c>
       <c r="AG12" t="n">
-        <v>118.06</v>
+        <v>101.63</v>
       </c>
       <c r="AH12" t="n">
-        <v>123.5</v>
+        <v>104.72</v>
       </c>
       <c r="AI12" t="n">
-        <v>129.14</v>
+        <v>107.9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>134.98</v>
+        <v>111.19</v>
       </c>
     </row>
     <row r="13">
@@ -2114,88 +2114,88 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1211.141463414634</v>
+        <v>1241.42</v>
       </c>
       <c r="J13" t="n">
-        <v>1241.42</v>
+        <v>1321.7</v>
       </c>
       <c r="K13" t="n">
-        <v>1273.32</v>
+        <v>1360.03</v>
       </c>
       <c r="L13" t="n">
-        <v>1306.05</v>
+        <v>1399.47</v>
       </c>
       <c r="M13" t="n">
-        <v>1339.61</v>
+        <v>1440.05</v>
       </c>
       <c r="N13" t="n">
-        <v>1374.04</v>
+        <v>1481.82</v>
       </c>
       <c r="O13" t="n">
-        <v>1409.36</v>
+        <v>1524.79</v>
       </c>
       <c r="P13" t="n">
-        <v>1445.58</v>
+        <v>1569.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>1482.73</v>
+        <v>1614.51</v>
       </c>
       <c r="R13" t="n">
-        <v>1520.83</v>
+        <v>1661.33</v>
       </c>
       <c r="S13" t="n">
-        <v>1559.92</v>
+        <v>1709.51</v>
       </c>
       <c r="T13" t="n">
-        <v>1600.01</v>
+        <v>1759.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1641.13</v>
+        <v>1810.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1667.55</v>
+        <v>1862.59</v>
       </c>
       <c r="W13" t="n">
-        <v>1694.4</v>
+        <v>1916.61</v>
       </c>
       <c r="X13" t="n">
-        <v>1721.68</v>
+        <v>1972.19</v>
       </c>
       <c r="Y13" t="n">
-        <v>1749.4</v>
+        <v>2029.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>1777.56</v>
+        <v>2088.23</v>
       </c>
       <c r="AA13" t="n">
-        <v>1806.18</v>
+        <v>2148.79</v>
       </c>
       <c r="AB13" t="n">
-        <v>1835.26</v>
+        <v>2211.11</v>
       </c>
       <c r="AC13" t="n">
-        <v>1864.81</v>
+        <v>2275.23</v>
       </c>
       <c r="AD13" t="n">
-        <v>1894.83</v>
+        <v>2341.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>1925.34</v>
+        <v>2409.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>1956.34</v>
+        <v>2478.97</v>
       </c>
       <c r="AG13" t="n">
-        <v>1987.83</v>
+        <v>2550.86</v>
       </c>
       <c r="AH13" t="n">
-        <v>2019.84</v>
+        <v>2624.83</v>
       </c>
       <c r="AI13" t="n">
-        <v>2052.36</v>
+        <v>2700.95</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2085.4</v>
+        <v>2779.28</v>
       </c>
     </row>
     <row r="14">
@@ -2238,88 +2238,88 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>20.69268292682927</v>
+        <v>20.33</v>
       </c>
       <c r="J14" t="n">
-        <v>21.21</v>
+        <v>23.37</v>
       </c>
       <c r="K14" t="n">
-        <v>22.25</v>
+        <v>24.05</v>
       </c>
       <c r="L14" t="n">
-        <v>23.33</v>
+        <v>24.83</v>
       </c>
       <c r="M14" t="n">
-        <v>24.46</v>
+        <v>25.71</v>
       </c>
       <c r="N14" t="n">
-        <v>25.63</v>
+        <v>26.66</v>
       </c>
       <c r="O14" t="n">
-        <v>26.86</v>
+        <v>27.68</v>
       </c>
       <c r="P14" t="n">
-        <v>28.13</v>
+        <v>28.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>29.46</v>
+        <v>29.92</v>
       </c>
       <c r="R14" t="n">
-        <v>30.84</v>
+        <v>31.16</v>
       </c>
       <c r="S14" t="n">
-        <v>32.29</v>
+        <v>32.47</v>
       </c>
       <c r="T14" t="n">
-        <v>33.79</v>
+        <v>33.89</v>
       </c>
       <c r="U14" t="n">
-        <v>35.35</v>
+        <v>35.38</v>
       </c>
       <c r="V14" t="n">
-        <v>37.1</v>
+        <v>36.94</v>
       </c>
       <c r="W14" t="n">
-        <v>38.9</v>
+        <v>38.56</v>
       </c>
       <c r="X14" t="n">
-        <v>40.77</v>
+        <v>40.27</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.7</v>
+        <v>42.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>44.7</v>
+        <v>43.89</v>
       </c>
       <c r="AA14" t="n">
-        <v>46.76</v>
+        <v>45.83</v>
       </c>
       <c r="AB14" t="n">
-        <v>48.89</v>
+        <v>47.86</v>
       </c>
       <c r="AC14" t="n">
-        <v>51.09</v>
+        <v>49.96</v>
       </c>
       <c r="AD14" t="n">
-        <v>53.37</v>
+        <v>52.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>55.72</v>
+        <v>54.47</v>
       </c>
       <c r="AF14" t="n">
-        <v>58.15</v>
+        <v>56.86</v>
       </c>
       <c r="AG14" t="n">
-        <v>60.66</v>
+        <v>59.37</v>
       </c>
       <c r="AH14" t="n">
-        <v>63.25</v>
+        <v>61.99</v>
       </c>
       <c r="AI14" t="n">
-        <v>65.93000000000001</v>
+        <v>64.73</v>
       </c>
       <c r="AJ14" t="n">
-        <v>68.69</v>
+        <v>67.58</v>
       </c>
     </row>
     <row r="15">
@@ -2362,88 +2362,88 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>53.81463414634146</v>
+        <v>51.8</v>
       </c>
       <c r="J15" t="n">
-        <v>55.16</v>
+        <v>45.01</v>
       </c>
       <c r="K15" t="n">
-        <v>58.36</v>
+        <v>48.08</v>
       </c>
       <c r="L15" t="n">
-        <v>61.73</v>
+        <v>48.83</v>
       </c>
       <c r="M15" t="n">
-        <v>65.27</v>
+        <v>50.42</v>
       </c>
       <c r="N15" t="n">
-        <v>69</v>
+        <v>52.46</v>
       </c>
       <c r="O15" t="n">
-        <v>72.93000000000001</v>
+        <v>54.86</v>
       </c>
       <c r="P15" t="n">
-        <v>77.05</v>
+        <v>57.54</v>
       </c>
       <c r="Q15" t="n">
-        <v>81.40000000000001</v>
+        <v>60.42</v>
       </c>
       <c r="R15" t="n">
-        <v>85.95999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="S15" t="n">
-        <v>90.77</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>95.81999999999999</v>
+        <v>69.53</v>
       </c>
       <c r="U15" t="n">
-        <v>101.13</v>
+        <v>72.66</v>
       </c>
       <c r="V15" t="n">
-        <v>106.96</v>
+        <v>75.86</v>
       </c>
       <c r="W15" t="n">
-        <v>113.04</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>119.39</v>
+        <v>83.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>126.03</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="Z15" t="n">
-        <v>132.95</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>140.17</v>
+        <v>94.91</v>
       </c>
       <c r="AB15" t="n">
-        <v>147.71</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>155.57</v>
+        <v>103.72</v>
       </c>
       <c r="AD15" t="n">
-        <v>163.78</v>
+        <v>108.43</v>
       </c>
       <c r="AE15" t="n">
-        <v>172.33</v>
+        <v>113.35</v>
       </c>
       <c r="AF15" t="n">
-        <v>181.25</v>
+        <v>118.49</v>
       </c>
       <c r="AG15" t="n">
-        <v>190.56</v>
+        <v>123.89</v>
       </c>
       <c r="AH15" t="n">
-        <v>200.25</v>
+        <v>129.51</v>
       </c>
       <c r="AI15" t="n">
-        <v>210.36</v>
+        <v>135.39</v>
       </c>
       <c r="AJ15" t="n">
-        <v>220.89</v>
+        <v>141.54</v>
       </c>
     </row>
     <row r="16">
@@ -2486,88 +2486,88 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>227.6682926829269</v>
+        <v>223.03</v>
       </c>
       <c r="J16" t="n">
-        <v>233.36</v>
+        <v>229.77</v>
       </c>
       <c r="K16" t="n">
-        <v>246.9</v>
+        <v>238.73</v>
       </c>
       <c r="L16" t="n">
-        <v>261.15</v>
+        <v>246.49</v>
       </c>
       <c r="M16" t="n">
-        <v>276.14</v>
+        <v>262.39</v>
       </c>
       <c r="N16" t="n">
-        <v>291.93</v>
+        <v>277.53</v>
       </c>
       <c r="O16" t="n">
-        <v>308.53</v>
+        <v>298.81</v>
       </c>
       <c r="P16" t="n">
-        <v>326</v>
+        <v>312.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>344.37</v>
+        <v>323.4</v>
       </c>
       <c r="R16" t="n">
-        <v>363.7</v>
+        <v>338.89</v>
       </c>
       <c r="S16" t="n">
-        <v>384.02</v>
+        <v>355.13</v>
       </c>
       <c r="T16" t="n">
-        <v>405.39</v>
+        <v>372.14</v>
       </c>
       <c r="U16" t="n">
-        <v>427.87</v>
+        <v>389.96</v>
       </c>
       <c r="V16" t="n">
-        <v>452.51</v>
+        <v>408.64</v>
       </c>
       <c r="W16" t="n">
-        <v>478.25</v>
+        <v>428.22</v>
       </c>
       <c r="X16" t="n">
-        <v>505.13</v>
+        <v>448.73</v>
       </c>
       <c r="Y16" t="n">
-        <v>533.1799999999999</v>
+        <v>470.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>562.47</v>
+        <v>492.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>593.04</v>
+        <v>516.35</v>
       </c>
       <c r="AB16" t="n">
-        <v>624.9299999999999</v>
+        <v>541.08</v>
       </c>
       <c r="AC16" t="n">
-        <v>658.2</v>
+        <v>567</v>
       </c>
       <c r="AD16" t="n">
-        <v>692.91</v>
+        <v>594.16</v>
       </c>
       <c r="AE16" t="n">
-        <v>729.1</v>
+        <v>622.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>766.85</v>
+        <v>652.4400000000001</v>
       </c>
       <c r="AG16" t="n">
-        <v>806.2</v>
+        <v>683.6900000000001</v>
       </c>
       <c r="AH16" t="n">
-        <v>847.22</v>
+        <v>716.4400000000001</v>
       </c>
       <c r="AI16" t="n">
-        <v>889.98</v>
+        <v>750.76</v>
       </c>
       <c r="AJ16" t="n">
-        <v>934.54</v>
+        <v>786.72</v>
       </c>
     </row>
     <row r="17">
@@ -2610,88 +2610,88 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>66.23414634146341</v>
+        <v>81.55</v>
       </c>
       <c r="J17" t="n">
-        <v>67.89</v>
+        <v>96.03</v>
       </c>
       <c r="K17" t="n">
-        <v>71.53</v>
+        <v>111.32</v>
       </c>
       <c r="L17" t="n">
-        <v>75.34</v>
+        <v>118.03</v>
       </c>
       <c r="M17" t="n">
-        <v>79.34</v>
+        <v>121.95</v>
       </c>
       <c r="N17" t="n">
-        <v>83.53</v>
+        <v>109.46</v>
       </c>
       <c r="O17" t="n">
-        <v>87.91</v>
+        <v>114.31</v>
       </c>
       <c r="P17" t="n">
-        <v>92.51000000000001</v>
+        <v>119.53</v>
       </c>
       <c r="Q17" t="n">
-        <v>97.31999999999999</v>
+        <v>126.06</v>
       </c>
       <c r="R17" t="n">
-        <v>102.35</v>
+        <v>133.15</v>
       </c>
       <c r="S17" t="n">
-        <v>107.63</v>
+        <v>140.42</v>
       </c>
       <c r="T17" t="n">
-        <v>113.15</v>
+        <v>147.69</v>
       </c>
       <c r="U17" t="n">
-        <v>118.93</v>
+        <v>155.15</v>
       </c>
       <c r="V17" t="n">
-        <v>125.51</v>
+        <v>162.24</v>
       </c>
       <c r="W17" t="n">
-        <v>132.36</v>
+        <v>170.07</v>
       </c>
       <c r="X17" t="n">
-        <v>139.5</v>
+        <v>177.73</v>
       </c>
       <c r="Y17" t="n">
-        <v>146.94</v>
+        <v>185.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>154.68</v>
+        <v>193.77</v>
       </c>
       <c r="AA17" t="n">
-        <v>162.73</v>
+        <v>200.86</v>
       </c>
       <c r="AB17" t="n">
-        <v>171.12</v>
+        <v>209.07</v>
       </c>
       <c r="AC17" t="n">
-        <v>179.85</v>
+        <v>214.72</v>
       </c>
       <c r="AD17" t="n">
-        <v>188.92</v>
+        <v>220.52</v>
       </c>
       <c r="AE17" t="n">
-        <v>198.37</v>
+        <v>226.45</v>
       </c>
       <c r="AF17" t="n">
-        <v>208.19</v>
+        <v>232.56</v>
       </c>
       <c r="AG17" t="n">
-        <v>218.41</v>
+        <v>238.84</v>
       </c>
       <c r="AH17" t="n">
-        <v>229.03</v>
+        <v>245.29</v>
       </c>
       <c r="AI17" t="n">
-        <v>240.08</v>
+        <v>251.91</v>
       </c>
       <c r="AJ17" t="n">
-        <v>251.56</v>
+        <v>258.69</v>
       </c>
     </row>
     <row r="18">
@@ -2734,88 +2734,88 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>28.97560975609756</v>
+        <v>27.95</v>
       </c>
       <c r="J18" t="n">
-        <v>29.7</v>
+        <v>29.35</v>
       </c>
       <c r="K18" t="n">
-        <v>31.04</v>
+        <v>30.91</v>
       </c>
       <c r="L18" t="n">
-        <v>32.42</v>
+        <v>33.61</v>
       </c>
       <c r="M18" t="n">
-        <v>33.86</v>
+        <v>35.12</v>
       </c>
       <c r="N18" t="n">
-        <v>35.36</v>
+        <v>36.47</v>
       </c>
       <c r="O18" t="n">
-        <v>36.91</v>
+        <v>38.12</v>
       </c>
       <c r="P18" t="n">
-        <v>38.52</v>
+        <v>40.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>40.19</v>
+        <v>42.81</v>
       </c>
       <c r="R18" t="n">
-        <v>41.92</v>
+        <v>44.83</v>
       </c>
       <c r="S18" t="n">
-        <v>43.72</v>
+        <v>47.08</v>
       </c>
       <c r="T18" t="n">
-        <v>45.59</v>
+        <v>49.36</v>
       </c>
       <c r="U18" t="n">
-        <v>47.52</v>
+        <v>51.77</v>
       </c>
       <c r="V18" t="n">
-        <v>49.72</v>
+        <v>55.4</v>
       </c>
       <c r="W18" t="n">
-        <v>51.99</v>
+        <v>57.97</v>
       </c>
       <c r="X18" t="n">
-        <v>54.33</v>
+        <v>60.58</v>
       </c>
       <c r="Y18" t="n">
-        <v>56.73</v>
+        <v>63.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>59.21</v>
+        <v>66.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>61.76</v>
+        <v>69.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>64.38</v>
+        <v>72.22</v>
       </c>
       <c r="AC18" t="n">
-        <v>67.09</v>
+        <v>75.47</v>
       </c>
       <c r="AD18" t="n">
-        <v>69.87</v>
+        <v>78.86</v>
       </c>
       <c r="AE18" t="n">
-        <v>72.73999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AF18" t="n">
-        <v>75.68000000000001</v>
+        <v>86.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>78.72</v>
+        <v>89.98</v>
       </c>
       <c r="AH18" t="n">
-        <v>81.84</v>
+        <v>94.03</v>
       </c>
       <c r="AI18" t="n">
-        <v>85.05</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="AJ18" t="n">
-        <v>88.36</v>
+        <v>102.67</v>
       </c>
     </row>
     <row r="19">
@@ -2858,88 +2858,88 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>49.67804878048781</v>
+        <v>50.51</v>
       </c>
       <c r="J19" t="n">
-        <v>50.92</v>
+        <v>54.68</v>
       </c>
       <c r="K19" t="n">
-        <v>52.61</v>
+        <v>55.94</v>
       </c>
       <c r="L19" t="n">
-        <v>54.35</v>
+        <v>57.22</v>
       </c>
       <c r="M19" t="n">
-        <v>56.13</v>
+        <v>60.48</v>
       </c>
       <c r="N19" t="n">
-        <v>57.95</v>
+        <v>61.87</v>
       </c>
       <c r="O19" t="n">
-        <v>59.81</v>
+        <v>62.9</v>
       </c>
       <c r="P19" t="n">
-        <v>61.72</v>
+        <v>63.97</v>
       </c>
       <c r="Q19" t="n">
-        <v>63.68</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>65.68000000000001</v>
+        <v>66.17</v>
       </c>
       <c r="S19" t="n">
-        <v>67.73</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>69.83</v>
+        <v>68.44</v>
       </c>
       <c r="U19" t="n">
-        <v>71.98</v>
+        <v>69.61</v>
       </c>
       <c r="V19" t="n">
-        <v>74.69</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>77.44</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>80.23999999999999</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="Y19" t="n">
-        <v>83.09999999999999</v>
+        <v>74.48</v>
       </c>
       <c r="Z19" t="n">
-        <v>86</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="AA19" t="n">
-        <v>88.95999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="AB19" t="n">
-        <v>91.97</v>
+        <v>78.39</v>
       </c>
       <c r="AC19" t="n">
-        <v>95.03</v>
+        <v>79.73</v>
       </c>
       <c r="AD19" t="n">
-        <v>98.15000000000001</v>
+        <v>81.11</v>
       </c>
       <c r="AE19" t="n">
-        <v>101.32</v>
+        <v>82.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>104.54</v>
+        <v>83.92</v>
       </c>
       <c r="AG19" t="n">
-        <v>107.83</v>
+        <v>85.37</v>
       </c>
       <c r="AH19" t="n">
-        <v>111.17</v>
+        <v>86.84</v>
       </c>
       <c r="AI19" t="n">
-        <v>114.57</v>
+        <v>88.33</v>
       </c>
       <c r="AJ19" t="n">
-        <v>118.03</v>
+        <v>89.84999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2982,10 +2982,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>6.204878048780489</v>
+        <v>3.13</v>
       </c>
       <c r="J20" t="n">
-        <v>6.36</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
         <v>6.67</v>
@@ -32682,4 +32682,225 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000F48F53D8446FB4EB61FD3AFE2640F25" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="83cf53e23258b582a307689f9bad4776">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7db9c71a-8f0f-4486-8c92-6242e053eab7" xmlns:ns3="8ae01698-3168-4e7f-b9e7-0ddc1c80de73" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8e6c764710efd91b3147b7c3b8958216" ns2:_="" ns3:_="">
+    <xsd:import namespace="7db9c71a-8f0f-4486-8c92-6242e053eab7"/>
+    <xsd:import namespace="8ae01698-3168-4e7f-b9e7-0ddc1c80de73"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7db9c71a-8f0f-4486-8c92-6242e053eab7" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8ae01698-3168-4e7f-b9e7-0ddc1c80de73" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{79606235-ded0-4d00-a81d-9caf851eecac}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="8ae01698-3168-4e7f-b9e7-0ddc1c80de73">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7db9c71a-8f0f-4486-8c92-6242e053eab7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8ae01698-3168-4e7f-b9e7-0ddc1c80de73" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80AF8FB7-C466-4731-AAE5-B3608CFFF035}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4527767A-4324-4744-A707-815401DFF112}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45161546-B1CE-4FBC-838D-2BCA86993291}"/>
 </file>
--- a/inputs/A1_Outputs/A1_Outputs_VGB/A-O_Demand.xlsx
+++ b/inputs/A1_Outputs/A1_Outputs_VGB/A-O_Demand.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Demand_Projection" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Profiles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand_Projection" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profiles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="0.000%"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,13 +70,22 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -112,7 +122,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -145,6 +155,13 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -32684,223 +32701,802 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000F48F53D8446FB4EB61FD3AFE2640F25" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="83cf53e23258b582a307689f9bad4776">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7db9c71a-8f0f-4486-8c92-6242e053eab7" xmlns:ns3="8ae01698-3168-4e7f-b9e7-0ddc1c80de73" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8e6c764710efd91b3147b7c3b8958216" ns2:_="" ns3:_="">
-    <xsd:import namespace="7db9c71a-8f0f-4486-8c92-6242e053eab7"/>
-    <xsd:import namespace="8ae01698-3168-4e7f-b9e7-0ddc1c80de73"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7db9c71a-8f0f-4486-8c92-6242e053eab7" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8ae01698-3168-4e7f-b9e7-0ddc1c80de73" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{79606235-ded0-4d00-a81d-9caf851eecac}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="8ae01698-3168-4e7f-b9e7-0ddc1c80de73">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7db9c71a-8f0f-4486-8c92-6242e053eab7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8ae01698-3168-4e7f-b9e7-0ddc1c80de73" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80AF8FB7-C466-4731-AAE5-B3608CFFF035}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4527767A-4324-4744-A707-815401DFF112}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45161546-B1CE-4FBC-838D-2BCA86993291}"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" style="4" min="1" max="1"/>
+    <col width="42" customWidth="1" style="4" min="2" max="2"/>
+    <col width="40" customWidth="1" style="4" min="3" max="3"/>
+    <col width="18" customWidth="1" style="4" min="4" max="4"/>
+    <col width="55" customWidth="1" style="4" min="5" max="5"/>
+    <col width="90" customWidth="1" style="4" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Fuentes de los datos de este libro. Las fuentes SUBRAYADAS son supuestos propios del equipo de modelación (no provienen de una fuente externa). Hoja informativa: el modelo no la lee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Hoja</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>Tecnologias</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>Parametro</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>Anios</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Demand_Projection</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>ELC{ISO}XX03 (demanda eléctrica de cada uno de los 19 países)</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>SpecifiedAnnualDemand</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>OLACDE – Generación eléctrica por fuente + OLACDE – Matriz de balance energético</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Demanda base (PJ) = generación eléctrica total del país en 2023 y 2024 (estadística anual de OLACDE, GWh × 0.0036) + importaciones − exportaciones de electricidad del mismo año (matriz de balance energético de OLACDE). Barbados no tiene interconexión: intercambio cero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Demand_Projection</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>ELC{ISO}XX03 (18 países; Haití se trata aparte)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>SpecifiedAnnualDemand</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Escenario de demanda alta de los documentos oficiales de planificación eléctrica de cada país (ver una fila por país)</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>Demanda(año) = demanda base OLACDE de 2024 × crecimiento acumulado, aplicando año a año la tasa de crecimiento del escenario de demanda alta de cada documento nacional. Bolivia, Ecuador, Nicaragua y Paraguay no publican un escenario alto: se usa su escenario central. Años fuera del horizonte del documento: se prolonga la tendencia con la tasa de crecimiento compuesta del tramo más cercano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Demand_Projection</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>ELCHTIXX03 (Haití)</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>SpecifiedAnnualDemand</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>IEA – World Energy Outlook 2025, escenario Net Zero Emissions (NZE) para los 19 países de la región</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>Haití no cuenta con un documento oficial de planificación en el conjunto de datos; se conserva la proyección de la IEA. Esto produce un salto de 3.35 a 6.67 PJ entre 2024 (dato OLACDE) y 2025 (dato IEA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Argentina – ELCARGXX03 e interconexiones de Argentina</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>ARG_LyE_para_ET_2050.pdf – Lineamientos y Escenarios para la Transición Energética al 2050 (Secretaría de Energía de Argentina)</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>Escenario Ambicioso (E3), Tabla 2, p. 38; el escenario central es el Escenario Base (E1). Tramo 2022-2030 común a ambos, sección 7.2.1, pp. 29-30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Bolivia – ELCBOLXX03 e interconexiones de Bolivia</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>BOL_PER_2035.pdf – Plan Eléctrico Referencial 2035 (Bolivia)</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Escenario Referencial, Tabla 8, pp. 34-36 y Anexo 4, p. 93. El documento no publica escenario alto: se usa el Referencial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Brasil – ELCBRAXX03 e interconexiones de Brasil</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>BRA_PDE2034_report.pdf – Plano Decenal de Expansão de Energia 2034 (EPE) y BRA_PNE2050.pdf – Plano Nacional de Energia 2050 (EPE)</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>Escenario alto: Cenário Superior del PDE 2034, Figura 2-23 / Box 2.2, p. 62 (4.0 % anual). Escenario central: Cenário de Referência, Tabela 2-3, p. 61, prolongado a 2050 con la Figura 9 del PNE 2050.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Barbados – ELCBRBXX03</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>BAR_ActionPlan_Roadmap_2030.pdf – Barbados Action Plan / Roadmap 2030</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>Escenario High, sección 6.2, p. 35 (el documento es narrativo, sin tabla numérica). Escenario central: Base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Chile – ELCCHLXX03 e interconexiones de Chile</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>CHL_PELP_2023-2027.pdf – Planificación Energética de Largo Plazo 2023-2027 (Ministerio de Energía de Chile)</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>Escenario Transición Acelerada, Figura 28 (valores leídos del gráfico). Escenario central: Carbono Neutralidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Colombia – ELCCOLXX03 e interconexiones de Colombia</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>COL_Plan_Generacion_2025-2039.pdf – Plan de Expansión de Referencia Generación 2025-2039 (UPME)</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>Escenario IC Superior 68 %, Tablas 32 y 33, pp. 93 y 95. Escenario central: Demanda Media, Tablas 13, 30 y 31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Costa Rica – ELCCRIXX03 e interconexiones de Costa Rica</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>CRI_PEG_2024-2040.pdf – Plan de Expansión de la Generación 2024-2040 (ICE)</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>Escenario Alta – Generación SEN, Tabla 6.2, pp. 60-61. Escenario central: Media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>República Dominicana – ELCDOMXX03 e interconexión con Haití</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>DOM_PEN_2022-2037.pdf – Plan Energético Nacional 2022-2037 (CNE)</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>Escenario Alternativo, capítulo 6.1.6, Tabla 182. Escenario central: Tendencial, Tabla 181.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Ecuador – ELCECUXX03 e interconexiones de Ecuador</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>ECU_PME_2023-2032.pdf – Plan Maestro de Electricidad 2023-2032 (Ecuador)</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>Hipótesis 2 – Caso Base (demanda en bornes de generación), capítulo 3, Tabla 3-26, p. 106. El documento no publica escenario alto: se usa el Caso Base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Guatemala – ELCGTMXX03 e interconexiones de Guatemala</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>GTM_PEG_2020-2050.pdf – Plan de Expansión de la Generación 2020-2050 (MEM / CNEE)</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>Escenario ALTO, Tabla 1, p. 35 (serie anual 2020-2050 en GWh). Escenario central: MEDIO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Honduras – ELCHNDXX03 e interconexiones de Honduras</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>HND_PIEG_2026-2035.pdf – Plan Indicativo de Expansión de la Generación 2026-2035 (y su anexo Anexos_HND_PIEG_2026-2035.pdf)</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>Escenario Alta IC 95 %, Tabla 26, p. 54 y Anexo Tabla C-3, p. 38. Escenario central: Media, Tabla 25 y Tabla C-2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Haití – ELCHTIXX03 (solo 2023-2024 con dato OLACDE)</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>Sin documento nacional; 2025-2050 según IEA World Energy Outlook 2025 (NZE)</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>Ver la fila de Haití en Demand_Projection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>México – ELCMEXXX03 e interconexión con Guatemala</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>MEX_PRODESEN_2024-2038_cap1-6.pdf – Programa de Desarrollo del Sistema Eléctrico Nacional 2024-2038 (SENER)</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>Escenario Alto, Cuadro 3.4, p. 63 (tasa media anual 2.9 %). Escenario central: Planeación, Cuadros 3.1, 3.4 y 3.5, pp. 38, 63 y 64 (consumo neto del SEN).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Nicaragua – ELCNICXX03 e interconexiones de Nicaragua</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>NIC_PIEG_2021-2035.pdf – Plan Indicativo de Expansión de la Generación 2021-2035 (MEM)</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>Demanda Media del SIN, Tabla 5, p. 10. El documento no publica escenario alto: se usa la Media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Panamá – ELCPANXX03 e interconexiones de Panamá</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>PAN_PESIN_2025-2039_TomoII.pdf – Plan de Expansión del Sistema Interconectado Nacional 2025-2039 Tomo II (ETESA)</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>Escenario Optimista-Alto, Tabla 2.1, p. 22. Escenario central: Moderado-Medio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Perú – ELCPERXX03 e interconexiones de Perú</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>PER_Anexo-D1_ProyeccionesDemandaFuturosExtremos.pdf – Anexo D.1 del Informe COES/DP-02-2022 (Plan de Transmisión del SEIN 2023-2032)</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>Escenario Muy Optimista, Tabla D.12, p. 12. Escenario central: Base, Tabla D.8, p. 10. El documento llega a 2032; el resto se prolonga con la misma tasa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Paraguay – ELCPRYXX03 e interconexiones de Paraguay</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>PRY_PlanMaestro_2024-2043.pdf – Plan Maestro de Generación 2024-2043 (ANDE)</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>Sección 4.1.2, Figura 4.7, curva DTM (valores leídos del gráfico; solo el año 2043 = 57 561 GWh está rotulado). El documento tiene una sola trayectoria de demanda: se usa como escenario alto y central.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>El Salvador – ELCSLVXX03 e interconexiones de El Salvador</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>SLV_PIEG_2024-2038.pdf – Plan Indicativo de la Expansión de la Generación 2024-2038 (CNE)</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>Demanda Alta, Tabla 14, pp. 46-47. Escenario central: Demanda Base, Tabla 8, pp. 34-35.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>Demanda por país (hoja Demand_Projection y escalamiento de interconexiones)</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Uruguay – ELCURYXX03 e interconexiones de Uruguay</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Crecimiento de la demanda – escenario alto</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>URY_PEG_2024-2043.pdf – Plan de Expansión de la Generación 2024-2043 (UTE)</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>Escenario PES nov/23 + Demanda 50 MW, Tabla I, sección 3.1, pp. 16-17. Escenario central: Incondicional + Demanda 50 MW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Profiles</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>ELC{ISO}{RR}01/02/03 (perfil horario de la demanda de cada país) × 12 bloques horarios</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>SpecifiedDemandProfile</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>2023-2050</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>OSeMOSYS Global (base de datos abierta del modelo eléctrico mundial OSeMOSYS Global)</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>Distribución de la demanda anual entre los 12 bloques horarios; normalizada para que la suma sea 1 en cada año.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/inputs/A1_Outputs/A1_Outputs_VGB/A-O_Demand.xlsx
+++ b/inputs/A1_Outputs/A1_Outputs_VGB/A-O_Demand.xlsx
@@ -33484,12 +33484,12 @@
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>OSeMOSYS Global (base de datos abierta del modelo eléctrico mundial OSeMOSYS Global)</t>
+          <t>Series horarias de demanda eléctrica de 2015 del conjunto de datos PLEXOS-World 2015 (Brinkerink et al., 2021), a través de OSeMOSYS Global</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>Distribución de la demanda anual entre los 12 bloques horarios; normalizada para que la suma sea 1 en cada año.</t>
+          <t>Perfil horario de la demanda de cada país en 2015: alrededor de la mitad de los perfiles proviene de datos históricos de los operadores de sistema y el resto se estimó a partir de países con características similares. OSeMOSYS Global suma las horas de cada bloque (estación × tramo del día) y normaliza para que la suma sea 1 en cada año; el mismo perfil se aplica a todos los años.</t>
         </is>
       </c>
     </row>

--- a/inputs/A1_Outputs/A1_Outputs_VGB/A-O_Demand.xlsx
+++ b/inputs/A1_Outputs/A1_Outputs_VGB/A-O_Demand.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand_Projection" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profiles" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Demand_Projection" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Profiles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fuentes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -32721,7 +32721,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>Fuentes de los datos de este libro. Las fuentes SUBRAYADAS son supuestos propios del equipo de modelación (no provienen de una fuente externa). Hoja informativa: el modelo no la lee.</t>
+          <t>Fuentes de los datos de este libro. Las fuentes marcadas como 'Supuesto propio' son estimaciones internas del equipo de modelación (no provienen de una fuente externa). Hoja informativa: el modelo no la lee.</t>
         </is>
       </c>
     </row>

--- a/inputs/A1_Outputs/A1_Outputs_VGB/A-O_Demand.xlsx
+++ b/inputs/A1_Outputs/A1_Outputs_VGB/A-O_Demand.xlsx
@@ -32743,7 +32743,7 @@
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>Anios</t>
+          <t>Años</t>
         </is>
       </c>
       <c r="E2" s="16" t="inlineStr">
